--- a/fake_db/BRCA_SNP.xlsx
+++ b/fake_db/BRCA_SNP.xlsx
@@ -702,12 +702,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -763,12 +766,9 @@
   </cellStyles>
   <dxfs count="18">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1244,7 +1244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="26.3636363636364" customWidth="1"/>
@@ -1340,9 +1340,72 @@
         <v>17</v>
       </c>
     </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="2"/>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="2"/>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="2"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="2"/>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="2"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="2"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="2"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="2"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="2"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A$1:A$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
